--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136441169</v>
       </c>
       <c r="B2" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136441073</v>
       </c>
       <c r="B16" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>136440929</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>136440948</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>136440959</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>136441276</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40414-2025 artfynd.xlsx
+++ b/artfynd/A 40414-2025 artfynd.xlsx
@@ -1226,7 +1226,7 @@
         <v>136439209</v>
       </c>
       <c r="B7" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>136439863</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>136440087</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
